--- a/public/storage/import_holiday.xlsx
+++ b/public/storage/import_holiday.xlsx
@@ -1,50 +1,111 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27531"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_DATA\itd.magang01\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EC0E1D-735D-4750-A88C-1285D39D68D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE7DD1C-EE71-4FE7-B393-5EB5E12FDFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="FORM_UPLOAD" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Contoh Pengisian Tanggal :
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>Tahun-bulan-tanggal
+2022-04-01</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>jenisizin</t>
+    <t>date_holiday</t>
   </si>
   <si>
-    <t>liburan kemana ya</t>
+    <t>note_holiday</t>
+  </si>
+  <si>
+    <t>2024-06-17</t>
+  </si>
+  <si>
+    <t>idul adha</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -56,8 +117,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44749F"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,16 +138,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -88,10 +155,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -395,102 +471,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7CE6B3-04B4-48C5-B45D-6D068181AC22}">
-  <dimension ref="A1:A28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/storage/import_holiday.xlsx
+++ b/public/storage/import_holiday.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_DATA\itd.magang01\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE7DD1C-EE71-4FE7-B393-5EB5E12FDFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881596C2-FC52-45E6-BD5A-13ED3829055E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,10 +61,10 @@
     <t>note_holiday</t>
   </si>
   <si>
-    <t>2024-06-17</t>
+    <t>2024-03-13</t>
   </si>
   <si>
-    <t>idul adha</t>
+    <t>Nyepi</t>
   </si>
 </sst>
 </file>
